--- a/AAII_Financials/Quarterly/INFQ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/INFQ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="92">
   <si>
     <t>INFQ</t>
   </si>
@@ -655,52 +655,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -719,29 +721,32 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E8" s="3">
         <v>9500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
+        <v>5300</v>
+      </c>
+      <c r="H8" s="3">
         <v>8300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>9300</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -760,29 +765,32 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E9" s="3">
         <v>7500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H9" s="3">
         <v>4900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>4200</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -801,29 +809,32 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E10" s="3">
         <v>2000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
+        <v>700</v>
+      </c>
+      <c r="H10" s="3">
         <v>3400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>5100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -842,8 +853,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -859,29 +873,30 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E12" s="3">
         <v>10000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
+        <v>5300</v>
+      </c>
+      <c r="H12" s="3">
         <v>5200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>4700</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -900,8 +915,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -941,13 +959,16 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>800</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -956,14 +977,14 @@
         <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -982,34 +1003,37 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
+        <v>900</v>
+      </c>
+      <c r="H15" s="3">
         <v>700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>800</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
@@ -1023,8 +1047,11 @@
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1037,29 +1064,30 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E17" s="3">
         <v>43000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>13700</v>
+      </c>
+      <c r="H17" s="3">
         <v>15300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>15700</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1078,29 +1106,32 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-33600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-11600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-7000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-6400</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1119,8 +1150,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1136,8 +1170,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1148,17 +1183,17 @@
         <v>-100</v>
       </c>
       <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>1700</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1177,34 +1212,37 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-27900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="H21" s="3">
         <v>-5600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7300</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
@@ -1218,8 +1256,11 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1259,29 +1300,32 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H23" s="3">
         <v>-6000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-8300</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,8 +1344,11 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1314,14 +1361,14 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1341,8 +1388,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1382,29 +1432,32 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-30300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H26" s="3">
         <v>-6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-8300</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1423,29 +1476,32 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-30300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H27" s="3">
         <v>-6000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-8300</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1464,8 +1520,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1505,8 +1564,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1531,8 +1593,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1546,8 +1608,11 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1587,8 +1652,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1628,8 +1696,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1640,17 +1711,17 @@
         <v>100</v>
       </c>
       <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>500</v>
+      </c>
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-1700</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,29 +1740,32 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-30300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-8300</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1710,8 +1784,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1751,29 +1828,32 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-30300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-8300</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1792,34 +1872,37 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1838,8 +1921,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1855,8 +1941,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1872,29 +1959,30 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E41" s="3">
         <v>84700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11700</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3">
         <v>47900</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1913,20 +2001,23 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>417700</v>
+      </c>
+      <c r="E42" s="3">
         <v>358900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>34300</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1939,8 +2030,8 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -1954,29 +2045,32 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E43" s="3">
         <v>12600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>7600</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1995,29 +2089,32 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E44" s="3">
         <v>4900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4300</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>2200</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,29 +2133,32 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>6400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2077,29 +2177,32 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>500300</v>
+      </c>
+      <c r="E46" s="3">
         <v>464900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74600</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3">
         <v>61000</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2118,20 +2221,23 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E47" s="3">
         <v>125100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17200</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2159,29 +2265,32 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E48" s="3">
         <v>12200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>14700</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2200,8 +2309,11 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2209,20 +2321,20 @@
         <v>9300</v>
       </c>
       <c r="E49" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F49" s="3">
         <v>9400</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>9400</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2241,8 +2353,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2282,8 +2397,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2323,29 +2441,32 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,8 +2485,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2405,29 +2529,32 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>641500</v>
+      </c>
+      <c r="E54" s="3">
         <v>612600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>115300</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3">
         <v>86300</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2446,8 +2573,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2463,8 +2593,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2480,29 +2611,30 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E57" s="3">
         <v>7200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7500</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>5300</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2521,29 +2653,32 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E58" s="3">
         <v>1100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1300</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2562,29 +2697,32 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E59" s="3">
         <v>12200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9900</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>7400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2603,29 +2741,32 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E60" s="3">
         <v>23600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>22700</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>16700</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2644,34 +2785,37 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>4800</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3" t="s">
-        <v>3</v>
+      <c r="K61" s="3">
+        <v>0</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>3</v>
@@ -2685,8 +2829,11 @@
       <c r="O61" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2699,15 +2846,15 @@
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,8 +2873,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2767,8 +2917,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2808,8 +2961,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2849,29 +3005,32 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E66" s="3">
         <v>27400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26700</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3">
         <v>21900</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2890,8 +3049,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2907,8 +3069,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2948,8 +3111,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2989,8 +3155,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2998,25 +3167,25 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>296800</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>247600</v>
       </c>
-      <c r="G70" s="3">
+      <c r="I70" s="3">
         <v>247600</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>3</v>
+      <c r="K70" s="3">
+        <v>0</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>3</v>
@@ -3030,8 +3199,11 @@
       <c r="O70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3071,29 +3243,32 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-287900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-261300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-231100</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>-199300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3112,8 +3287,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3153,8 +3331,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3194,8 +3375,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3235,29 +3419,32 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>574400</v>
+      </c>
+      <c r="E76" s="3">
         <v>585300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-208200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3">
         <v>-183200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-183200</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,8 +3463,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3317,34 +3507,37 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3363,29 +3556,32 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-30300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-8300</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,8 +3600,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3421,16 +3620,17 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>800</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -3462,8 +3662,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3503,8 +3706,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3544,8 +3750,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3585,8 +3794,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3626,8 +3838,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3667,29 +3882,32 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H89" s="3">
         <v>-7000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2900</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3708,8 +3926,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3725,29 +3946,30 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3766,8 +3988,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3807,8 +4032,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3848,29 +4076,32 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-433100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3889,8 +4120,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3906,8 +4140,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3947,8 +4182,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3988,8 +4226,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4029,8 +4270,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4070,29 +4314,32 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E100" s="3">
         <v>525200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>49600</v>
+      </c>
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>25400</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4111,16 +4358,19 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>200</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -4152,34 +4402,37 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E102" s="3">
         <v>73000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
+        <v>46600</v>
+      </c>
+      <c r="H102" s="3">
         <v>-7000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>21900</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -4191,6 +4444,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
